--- a/LR2.xlsx
+++ b/LR2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\IT_in_PA\25VVV3\3_GS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FD428F-6E97-48D8-9740-1F1B72B1935D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DBD080-6241-482F-A8DB-51B7F09DA537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -617,7 +617,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1200</c:v>
@@ -850,7 +850,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1200</c:v>
@@ -1196,7 +1196,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1200</c:v>
@@ -1269,7 +1269,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>350000</c:v>
+                  <c:v>280000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>420000</c:v>
@@ -1359,7 +1359,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>192500.00000000003</c:v>
+                  <c:v>154000</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>231000.00000000003</c:v>
@@ -1697,7 +1697,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2315,7 +2315,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1000</c:v>
+                  <c:v>800</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1200</c:v>
@@ -5338,7 +5338,7 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="C7">
         <v>1200</v>
@@ -5359,7 +5359,7 @@
       </c>
       <c r="B8">
         <f>$B$3*B7</f>
-        <v>350000</v>
+        <v>280000</v>
       </c>
       <c r="C8">
         <f>$B$3*C7</f>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="B9">
         <f>(1-$B$5)*B8</f>
-        <v>192500.00000000003</v>
+        <v>154000</v>
       </c>
       <c r="C9">
         <f>(1-$B$5)*C8</f>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="B10">
         <f>$B$4*B7</f>
-        <v>80000</v>
+        <v>64000</v>
       </c>
       <c r="C10">
         <f>$B$4*C7</f>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="B12">
         <f>B8-(B9+B10)</f>
-        <v>77500</v>
+        <v>62000</v>
       </c>
       <c r="C12">
         <f>C8-(C9+C10)</f>
